--- a/exports/HR_Analytics_Report.xlsx
+++ b/exports/HR_Analytics_Report.xlsx
@@ -456,11 +456,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rahul1</t>
+          <t>Asha1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,11 +469,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>75184</v>
+        <v>88247</v>
       </c>
     </row>
     <row r="3">
@@ -482,15 +482,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kiran2</t>
+          <t>Meena2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>36174</v>
+        <v>54032</v>
       </c>
     </row>
     <row r="4">
@@ -508,15 +508,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Divya3</t>
+          <t>Asha3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>60978</v>
+        <v>43524</v>
       </c>
     </row>
     <row r="5">
@@ -534,24 +534,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ravi4</t>
+          <t>Kiran4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>83470</v>
+        <v>56257</v>
       </c>
     </row>
     <row r="6">
@@ -560,24 +560,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meena5</t>
+          <t>Divya5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>70366</v>
+        <v>33224</v>
       </c>
     </row>
     <row r="7">
@@ -586,24 +586,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Priya6</t>
+          <t>Asha6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>54085</v>
+        <v>87885</v>
       </c>
     </row>
     <row r="8">
@@ -612,24 +612,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rahul7</t>
+          <t>Anu7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>53794</v>
+        <v>49895</v>
       </c>
     </row>
     <row r="9">
@@ -638,24 +638,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>John8</t>
+          <t>Kiran8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>88985</v>
+        <v>54707</v>
       </c>
     </row>
     <row r="10">
@@ -664,24 +664,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anu9</t>
+          <t>Arun9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>49548</v>
+        <v>40748</v>
       </c>
     </row>
     <row r="11">
@@ -690,24 +690,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rahul10</t>
+          <t>Ravi10</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>88528</v>
+        <v>55654</v>
       </c>
     </row>
     <row r="12">
@@ -720,20 +720,20 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>68201</v>
+        <v>30943</v>
       </c>
     </row>
     <row r="13">
@@ -742,24 +742,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>John12</t>
+          <t>Arun12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>69715</v>
+        <v>49482</v>
       </c>
     </row>
     <row r="14">
@@ -768,11 +768,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ravi13</t>
+          <t>Arun13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -781,11 +781,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>63506</v>
+        <v>76696</v>
       </c>
     </row>
     <row r="15">
@@ -794,11 +794,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Divya14</t>
+          <t>Ravi14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -807,11 +807,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>68171</v>
+        <v>36331</v>
       </c>
     </row>
     <row r="16">
@@ -820,24 +820,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kiran15</t>
+          <t>Anu15</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>40801</v>
+        <v>47466</v>
       </c>
     </row>
     <row r="17">
@@ -846,24 +846,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arun16</t>
+          <t>Priya16</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>82914</v>
+        <v>69886</v>
       </c>
     </row>
     <row r="18">
@@ -872,24 +872,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Priya17</t>
+          <t>Ravi17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>49754</v>
+        <v>66537</v>
       </c>
     </row>
     <row r="19">
@@ -898,24 +898,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rahul18</t>
+          <t>Meena18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>36971</v>
+        <v>71141</v>
       </c>
     </row>
     <row r="20">
@@ -924,11 +924,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ravi19</t>
+          <t>Kiran19</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>77879</v>
+        <v>58486</v>
       </c>
     </row>
     <row r="21">
@@ -950,24 +950,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Asha20</t>
+          <t>Divya20</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Team Lead</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>71492</v>
+        <v>48913</v>
       </c>
     </row>
     <row r="22">
@@ -976,15 +976,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Asha21</t>
+          <t>Ravi21</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>42744</v>
+        <v>49296</v>
       </c>
     </row>
     <row r="23">
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arun22</t>
+          <t>Anu22</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>85740</v>
+        <v>73751</v>
       </c>
     </row>
     <row r="24">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arun23</t>
+          <t>Asha23</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1041,11 +1041,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>67234</v>
+        <v>79194</v>
       </c>
     </row>
     <row r="25">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kiran24</t>
+          <t>Arun24</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>65911</v>
+        <v>84706</v>
       </c>
     </row>
     <row r="26">
@@ -1080,24 +1080,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arun25</t>
+          <t>Kiran25</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>71912</v>
+        <v>85708</v>
       </c>
     </row>
     <row r="27">
@@ -1106,24 +1106,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ravi26</t>
+          <t>Divya26</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>87456</v>
+        <v>89391</v>
       </c>
     </row>
     <row r="28">
@@ -1132,24 +1132,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rahul27</t>
+          <t>Anu27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>58043</v>
+        <v>72545</v>
       </c>
     </row>
     <row r="29">
@@ -1158,24 +1158,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>John28</t>
+          <t>Kiran28</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>85121</v>
+        <v>30161</v>
       </c>
     </row>
     <row r="30">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Meena29</t>
+          <t>Divya29</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>77542</v>
+        <v>69412</v>
       </c>
     </row>
     <row r="31">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1223,11 +1223,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Team Lead</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>86960</v>
+        <v>79608</v>
       </c>
     </row>
     <row r="32">
@@ -1236,24 +1236,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kiran31</t>
+          <t>Rahul31</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>85113</v>
+        <v>42896</v>
       </c>
     </row>
     <row r="33">
@@ -1266,20 +1266,20 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>72502</v>
+        <v>70669</v>
       </c>
     </row>
     <row r="34">
@@ -1288,15 +1288,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ravi33</t>
+          <t>Kiran33</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>89260</v>
+        <v>47595</v>
       </c>
     </row>
     <row r="35">
@@ -1314,24 +1314,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Divya34</t>
+          <t>Asha34</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>41082</v>
+        <v>72835</v>
       </c>
     </row>
     <row r="36">
@@ -1340,15 +1340,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Asha35</t>
+          <t>Ravi35</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>58307</v>
+        <v>41176</v>
       </c>
     </row>
     <row r="37">
@@ -1366,24 +1366,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kiran36</t>
+          <t>Meena36</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Team Lead</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>82521</v>
+        <v>76468</v>
       </c>
     </row>
     <row r="38">
@@ -1392,24 +1392,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Meena37</t>
+          <t>Ravi37</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>67223</v>
+        <v>88707</v>
       </c>
     </row>
     <row r="39">
@@ -1418,15 +1418,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Asha38</t>
+          <t>Ravi38</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>30617</v>
+        <v>49070</v>
       </c>
     </row>
     <row r="40">
@@ -1444,24 +1444,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kiran39</t>
+          <t>Anu39</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>35021</v>
+        <v>31493</v>
       </c>
     </row>
     <row r="41">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1483,11 +1483,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>78190</v>
+        <v>41384</v>
       </c>
     </row>
     <row r="42">
@@ -1496,24 +1496,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Arun41</t>
+          <t>Kiran41</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>53838</v>
+        <v>85604</v>
       </c>
     </row>
     <row r="43">
@@ -1522,24 +1522,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>John42</t>
+          <t>Asha42</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>54168</v>
+        <v>48219</v>
       </c>
     </row>
     <row r="44">
@@ -1548,11 +1548,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>John43</t>
+          <t>Kiran43</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1561,11 +1561,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>83808</v>
+        <v>45393</v>
       </c>
     </row>
     <row r="45">
@@ -1574,24 +1574,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Priya44</t>
+          <t>Ravi44</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>42494</v>
+        <v>65740</v>
       </c>
     </row>
     <row r="46">
@@ -1600,24 +1600,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ravi45</t>
+          <t>John45</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>40304</v>
+        <v>66905</v>
       </c>
     </row>
     <row r="47">
@@ -1626,15 +1626,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Divya46</t>
+          <t>Rahul46</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>40224</v>
+        <v>61022</v>
       </c>
     </row>
     <row r="48">
@@ -1652,11 +1652,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Arun47</t>
+          <t>Anu47</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1665,11 +1665,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>79188</v>
+        <v>35173</v>
       </c>
     </row>
     <row r="49">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>56279</v>
+        <v>78208</v>
       </c>
     </row>
     <row r="50">
@@ -1704,24 +1704,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rahul49</t>
+          <t>Arun49</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>33537</v>
+        <v>85644</v>
       </c>
     </row>
     <row r="51">
@@ -1730,24 +1730,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rahul50</t>
+          <t>John50</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>83619</v>
+        <v>53051</v>
       </c>
     </row>
     <row r="52">
@@ -1756,11 +1756,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Arun51</t>
+          <t>Priya51</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1769,11 +1769,11 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>59975</v>
+        <v>45878</v>
       </c>
     </row>
     <row r="53">
@@ -1782,11 +1782,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ravi52</t>
+          <t>Anu52</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1795,11 +1795,11 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>57409</v>
+        <v>86429</v>
       </c>
     </row>
     <row r="54">
@@ -1808,24 +1808,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kiran53</t>
+          <t>Meena53</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>80477</v>
+        <v>76386</v>
       </c>
     </row>
     <row r="55">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>65476</v>
+        <v>77096</v>
       </c>
     </row>
     <row r="56">
@@ -1860,24 +1860,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Anu55</t>
+          <t>Priya55</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>87091</v>
+        <v>58146</v>
       </c>
     </row>
     <row r="57">
@@ -1886,15 +1886,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Divya56</t>
+          <t>John56</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>63112</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="58">
@@ -1912,24 +1912,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kiran57</t>
+          <t>John57</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>73795</v>
+        <v>69678</v>
       </c>
     </row>
     <row r="59">
@@ -1942,20 +1942,20 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>44372</v>
+        <v>57944</v>
       </c>
     </row>
     <row r="60">
@@ -1964,24 +1964,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ravi59</t>
+          <t>Divya59</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>76265</v>
+        <v>71744</v>
       </c>
     </row>
     <row r="61">
@@ -1990,24 +1990,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ravi60</t>
+          <t>Arun60</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>70367</v>
+        <v>55673</v>
       </c>
     </row>
     <row r="62">
@@ -2016,24 +2016,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Anu61</t>
+          <t>Kiran61</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>75907</v>
+        <v>33081</v>
       </c>
     </row>
     <row r="63">
@@ -2042,11 +2042,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ravi62</t>
+          <t>Meena62</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>64036</v>
+        <v>82042</v>
       </c>
     </row>
     <row r="64">
@@ -2072,20 +2072,20 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>81046</v>
+        <v>41265</v>
       </c>
     </row>
     <row r="65">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Divya64</t>
+          <t>Arun64</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>32316</v>
+        <v>37308</v>
       </c>
     </row>
     <row r="66">
@@ -2120,24 +2120,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rahul65</t>
+          <t>Divya65</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>84181</v>
+        <v>77352</v>
       </c>
     </row>
     <row r="67">
@@ -2146,11 +2146,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>John66</t>
+          <t>Rahul66</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2159,11 +2159,11 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>79502</v>
+        <v>38434</v>
       </c>
     </row>
     <row r="68">
@@ -2172,11 +2172,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rahul67</t>
+          <t>Divya67</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2185,11 +2185,11 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>30647</v>
+        <v>71794</v>
       </c>
     </row>
     <row r="69">
@@ -2202,20 +2202,20 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Team Lead</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>67049</v>
+        <v>53223</v>
       </c>
     </row>
     <row r="70">
@@ -2224,24 +2224,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kiran69</t>
+          <t>Asha69</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>50625</v>
+        <v>79907</v>
       </c>
     </row>
     <row r="71">
@@ -2250,15 +2250,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Asha70</t>
+          <t>John70</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>83190</v>
+        <v>61437</v>
       </c>
     </row>
     <row r="72">
@@ -2276,24 +2276,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kiran71</t>
+          <t>Ravi71</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>30121</v>
+        <v>30966</v>
       </c>
     </row>
     <row r="73">
@@ -2302,24 +2302,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Anu72</t>
+          <t>Rahul72</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Team Lead</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>88754</v>
+        <v>46876</v>
       </c>
     </row>
     <row r="74">
@@ -2328,24 +2328,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ravi73</t>
+          <t>Rahul73</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>87142</v>
+        <v>47117</v>
       </c>
     </row>
     <row r="75">
@@ -2354,24 +2354,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>John74</t>
+          <t>Arun74</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>54179</v>
+        <v>36577</v>
       </c>
     </row>
     <row r="76">
@@ -2380,24 +2380,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Asha75</t>
+          <t>Ravi75</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>51914</v>
+        <v>60851</v>
       </c>
     </row>
     <row r="77">
@@ -2406,24 +2406,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Meena76</t>
+          <t>Rahul76</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Team Lead</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>31154</v>
+        <v>83942</v>
       </c>
     </row>
     <row r="78">
@@ -2432,15 +2432,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Priya77</t>
+          <t>John77</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>56461</v>
+        <v>49866</v>
       </c>
     </row>
     <row r="79">
@@ -2458,11 +2458,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Priya78</t>
+          <t>Rahul78</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2471,11 +2471,11 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>52170</v>
+        <v>68289</v>
       </c>
     </row>
     <row r="80">
@@ -2484,24 +2484,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rahul79</t>
+          <t>Meena79</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>70083</v>
+        <v>71987</v>
       </c>
     </row>
     <row r="81">
@@ -2510,11 +2510,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ravi80</t>
+          <t>Rahul80</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2523,11 +2523,11 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>62641</v>
+        <v>71502</v>
       </c>
     </row>
     <row r="82">
@@ -2536,24 +2536,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Arun81</t>
+          <t>Ravi81</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Team Lead</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>87293</v>
+        <v>68315</v>
       </c>
     </row>
     <row r="83">
@@ -2562,11 +2562,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Rahul82</t>
+          <t>Ravi82</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>48344</v>
+        <v>84596</v>
       </c>
     </row>
     <row r="84">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Arun83</t>
+          <t>Kiran83</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>61944</v>
+        <v>47146</v>
       </c>
     </row>
     <row r="85">
@@ -2614,24 +2614,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Arun84</t>
+          <t>Anu84</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>30903</v>
+        <v>56753</v>
       </c>
     </row>
     <row r="86">
@@ -2640,11 +2640,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Divya85</t>
+          <t>Arun85</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2653,11 +2653,11 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Team Lead</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>76849</v>
+        <v>78327</v>
       </c>
     </row>
     <row r="87">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Asha86</t>
+          <t>Meena86</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>63944</v>
+        <v>81753</v>
       </c>
     </row>
     <row r="88">
@@ -2692,24 +2692,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Meena87</t>
+          <t>Kiran87</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>33511</v>
+        <v>54419</v>
       </c>
     </row>
     <row r="89">
@@ -2718,24 +2718,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ravi88</t>
+          <t>Priya88</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>52552</v>
+        <v>84308</v>
       </c>
     </row>
     <row r="90">
@@ -2744,11 +2744,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Anu89</t>
+          <t>Ravi89</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2757,11 +2757,11 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>87078</v>
+        <v>66491</v>
       </c>
     </row>
     <row r="91">
@@ -2770,24 +2770,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Asha90</t>
+          <t>Divya90</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>32271</v>
+        <v>70862</v>
       </c>
     </row>
     <row r="92">
@@ -2796,24 +2796,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Rahul91</t>
+          <t>Asha91</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>46925</v>
+        <v>41653</v>
       </c>
     </row>
     <row r="93">
@@ -2822,24 +2822,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Anu92</t>
+          <t>Divya92</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>72139</v>
+        <v>58661</v>
       </c>
     </row>
     <row r="94">
@@ -2848,11 +2848,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Anu93</t>
+          <t>Asha93</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2861,11 +2861,11 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>47020</v>
+        <v>48467</v>
       </c>
     </row>
     <row r="95">
@@ -2874,24 +2874,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Rahul94</t>
+          <t>Asha94</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>64226</v>
+        <v>70134</v>
       </c>
     </row>
     <row r="96">
@@ -2900,24 +2900,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Anu95</t>
+          <t>Divya95</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>32590</v>
+        <v>35500</v>
       </c>
     </row>
     <row r="97">
@@ -2926,24 +2926,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Meena96</t>
+          <t>Asha96</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>52125</v>
+        <v>34825</v>
       </c>
     </row>
     <row r="98">
@@ -2952,24 +2952,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Divya97</t>
+          <t>John97</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>31927</v>
+        <v>40117</v>
       </c>
     </row>
     <row r="99">
@@ -2978,24 +2978,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Meena98</t>
+          <t>Anu98</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>60323</v>
+        <v>55542</v>
       </c>
     </row>
     <row r="100">
@@ -3004,24 +3004,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Priya99</t>
+          <t>Ravi99</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Team Lead</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>42630</v>
+        <v>48136</v>
       </c>
     </row>
     <row r="101">
@@ -3030,24 +3030,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>John100</t>
+          <t>Anu100</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Team Lead</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>67950</v>
+        <v>37705</v>
       </c>
     </row>
   </sheetData>
@@ -3114,19 +3114,19 @@
         <v>90</v>
       </c>
       <c r="C2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>7.548333333333334</v>
+        <v>7.468111111111111</v>
       </c>
       <c r="G2" t="n">
-        <v>92.22222222222224</v>
+        <v>93.33333333333331</v>
       </c>
       <c r="H2" t="n">
         <v>5</v>
@@ -3140,22 +3140,22 @@
         <v>90</v>
       </c>
       <c r="C3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>7.420777777777777</v>
+        <v>7.454</v>
       </c>
       <c r="G3" t="n">
-        <v>97.77777777777776</v>
+        <v>98.88888888888889</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3166,22 +3166,22 @@
         <v>90</v>
       </c>
       <c r="C4" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>7.658222222222222</v>
+        <v>7.533222222222222</v>
       </c>
       <c r="G4" t="n">
-        <v>95.55555555555556</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -3192,19 +3192,19 @@
         <v>90</v>
       </c>
       <c r="C5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>7.409777777777777</v>
+        <v>7.480333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>91.11111111111111</v>
+        <v>92.22222222222224</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -3218,22 +3218,22 @@
         <v>90</v>
       </c>
       <c r="C6" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>7.465888888888889</v>
+        <v>7.473555555555556</v>
       </c>
       <c r="G6" t="n">
-        <v>92.22222222222224</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3244,22 +3244,22 @@
         <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>7.426111111111111</v>
+        <v>7.592222222222221</v>
       </c>
       <c r="G7" t="n">
-        <v>93.33333333333331</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -3270,22 +3270,22 @@
         <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>7.466666666666667</v>
+        <v>7.486888888888889</v>
       </c>
       <c r="G8" t="n">
-        <v>98.88888888888889</v>
+        <v>91.11111111111111</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3296,22 +3296,22 @@
         <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
-        <v>7.334888888888889</v>
+        <v>7.394555555555556</v>
       </c>
       <c r="G9" t="n">
-        <v>95.55555555555556</v>
+        <v>91.11111111111111</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3322,22 +3322,22 @@
         <v>90</v>
       </c>
       <c r="C10" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>7.391000000000001</v>
+        <v>7.678888888888889</v>
       </c>
       <c r="G10" t="n">
-        <v>98.88888888888889</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -3348,22 +3348,22 @@
         <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>7.401555555555555</v>
+        <v>7.541111111111111</v>
       </c>
       <c r="G11" t="n">
-        <v>93.33333333333331</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3380,16 +3380,16 @@
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>7.403777777777778</v>
+        <v>7.481444444444445</v>
       </c>
       <c r="G12" t="n">
         <v>95.55555555555556</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -3400,19 +3400,19 @@
         <v>90</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>7.334444444444444</v>
+        <v>7.45611111111111</v>
       </c>
       <c r="G13" t="n">
-        <v>96.66666666666669</v>
+        <v>91.11111111111111</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
@@ -3426,22 +3426,22 @@
         <v>90</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F14" t="n">
-        <v>7.440555555555555</v>
+        <v>7.554222222222222</v>
       </c>
       <c r="G14" t="n">
-        <v>97.77777777777776</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -3458,16 +3458,16 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" t="n">
-        <v>7.407</v>
+        <v>7.494333333333333</v>
       </c>
       <c r="G15" t="n">
         <v>94.44444444444444</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -3478,22 +3478,22 @@
         <v>90</v>
       </c>
       <c r="C16" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F16" t="n">
-        <v>7.452333333333334</v>
+        <v>7.598444444444445</v>
       </c>
       <c r="G16" t="n">
-        <v>92.22222222222224</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -3504,22 +3504,22 @@
         <v>90</v>
       </c>
       <c r="C17" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F17" t="n">
-        <v>7.451222222222222</v>
+        <v>7.561666666666666</v>
       </c>
       <c r="G17" t="n">
-        <v>94.44444444444444</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3530,22 +3530,22 @@
         <v>90</v>
       </c>
       <c r="C18" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>54</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7.447888888888889</v>
+      </c>
+      <c r="G18" t="n">
+        <v>93.33333333333331</v>
+      </c>
+      <c r="H18" t="n">
         <v>4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>58</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7.408</v>
-      </c>
-      <c r="G18" t="n">
-        <v>95.55555555555556</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3556,22 +3556,22 @@
         <v>90</v>
       </c>
       <c r="C19" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F19" t="n">
-        <v>7.435777777777778</v>
+        <v>7.436888888888889</v>
       </c>
       <c r="G19" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -3582,22 +3582,22 @@
         <v>90</v>
       </c>
       <c r="C20" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F20" t="n">
-        <v>7.417111111111111</v>
+        <v>7.511777777777777</v>
       </c>
       <c r="G20" t="n">
-        <v>91.11111111111111</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -3608,19 +3608,19 @@
         <v>90</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>7.326999999999999</v>
+        <v>7.689333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>94.44444444444444</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
@@ -3634,22 +3634,22 @@
         <v>90</v>
       </c>
       <c r="C22" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F22" t="n">
-        <v>7.447</v>
+        <v>7.632888888888889</v>
       </c>
       <c r="G22" t="n">
-        <v>98.88888888888889</v>
+        <v>90</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -3660,22 +3660,22 @@
         <v>90</v>
       </c>
       <c r="C23" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>7.590888888888888</v>
+        <v>7.532222222222222</v>
       </c>
       <c r="G23" t="n">
-        <v>92.22222222222224</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -3686,22 +3686,22 @@
         <v>90</v>
       </c>
       <c r="C24" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F24" t="n">
-        <v>7.448111111111111</v>
+        <v>7.492555555555556</v>
       </c>
       <c r="G24" t="n">
-        <v>95.55555555555556</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -3712,22 +3712,22 @@
         <v>90</v>
       </c>
       <c r="C25" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>58</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7.490777777777778</v>
+      </c>
+      <c r="G25" t="n">
+        <v>98.88888888888889</v>
+      </c>
+      <c r="H25" t="n">
         <v>3</v>
-      </c>
-      <c r="E25" t="n">
-        <v>52</v>
-      </c>
-      <c r="F25" t="n">
-        <v>7.537666666666666</v>
-      </c>
-      <c r="G25" t="n">
-        <v>96.66666666666669</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -3738,22 +3738,22 @@
         <v>90</v>
       </c>
       <c r="C26" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>7.533333333333333</v>
+        <v>7.494444444444444</v>
       </c>
       <c r="G26" t="n">
-        <v>93.33333333333331</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -3764,22 +3764,22 @@
         <v>90</v>
       </c>
       <c r="C27" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>7.476777777777778</v>
+        <v>7.646</v>
       </c>
       <c r="G27" t="n">
-        <v>95.55555555555556</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -3790,22 +3790,22 @@
         <v>90</v>
       </c>
       <c r="C28" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
-        <v>7.442888888888889</v>
+        <v>7.409000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>96.66666666666669</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3816,19 +3816,19 @@
         <v>90</v>
       </c>
       <c r="C29" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F29" t="n">
-        <v>7.514666666666667</v>
+        <v>7.559111111111112</v>
       </c>
       <c r="G29" t="n">
-        <v>96.66666666666669</v>
+        <v>93.33333333333331</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
@@ -3842,19 +3842,19 @@
         <v>90</v>
       </c>
       <c r="C30" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F30" t="n">
-        <v>7.370999999999999</v>
+        <v>7.549666666666667</v>
       </c>
       <c r="G30" t="n">
-        <v>97.77777777777776</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -3868,19 +3868,19 @@
         <v>90</v>
       </c>
       <c r="C31" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F31" t="n">
-        <v>7.436333333333333</v>
+        <v>7.518111111111111</v>
       </c>
       <c r="G31" t="n">
-        <v>94.44444444444444</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H31" t="n">
         <v>2</v>
@@ -3900,16 +3900,16 @@
         <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F32" t="n">
-        <v>7.444999999999999</v>
+        <v>7.544111111111111</v>
       </c>
       <c r="G32" t="n">
         <v>94.44444444444444</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -3926,16 +3926,16 @@
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>7.552555555555556</v>
+        <v>7.412777777777777</v>
       </c>
       <c r="G33" t="n">
         <v>96.66666666666669</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3946,22 +3946,22 @@
         <v>90</v>
       </c>
       <c r="C34" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F34" t="n">
-        <v>7.398444444444444</v>
+        <v>7.534555555555555</v>
       </c>
       <c r="G34" t="n">
-        <v>94.44444444444444</v>
+        <v>93.33333333333331</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -3972,19 +3972,19 @@
         <v>90</v>
       </c>
       <c r="C35" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F35" t="n">
-        <v>7.373</v>
+        <v>7.516222222222223</v>
       </c>
       <c r="G35" t="n">
-        <v>92.22222222222224</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H35" t="n">
         <v>4</v>
@@ -4004,16 +4004,16 @@
         <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F36" t="n">
-        <v>7.465888888888888</v>
+        <v>7.360333333333333</v>
       </c>
       <c r="G36" t="n">
         <v>94.44444444444444</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -4024,22 +4024,22 @@
         <v>90</v>
       </c>
       <c r="C37" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
-        <v>7.396</v>
+        <v>7.604222222222222</v>
       </c>
       <c r="G37" t="n">
-        <v>98.88888888888889</v>
+        <v>93.33333333333331</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -4050,22 +4050,22 @@
         <v>90</v>
       </c>
       <c r="C38" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F38" t="n">
-        <v>7.459222222222222</v>
+        <v>7.568555555555555</v>
       </c>
       <c r="G38" t="n">
-        <v>98.88888888888889</v>
+        <v>100</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -4082,16 +4082,16 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F39" t="n">
-        <v>7.507222222222222</v>
+        <v>7.479333333333333</v>
       </c>
       <c r="G39" t="n">
         <v>93.33333333333331</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -4102,22 +4102,22 @@
         <v>90</v>
       </c>
       <c r="C40" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F40" t="n">
-        <v>7.426888888888889</v>
+        <v>7.438777777777778</v>
       </c>
       <c r="G40" t="n">
-        <v>92.22222222222224</v>
+        <v>91.11111111111111</v>
       </c>
       <c r="H40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -4128,22 +4128,22 @@
         <v>90</v>
       </c>
       <c r="C41" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F41" t="n">
-        <v>7.480666666666666</v>
+        <v>7.593555555555555</v>
       </c>
       <c r="G41" t="n">
-        <v>91.11111111111111</v>
+        <v>98.88888888888889</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -4154,22 +4154,22 @@
         <v>90</v>
       </c>
       <c r="C42" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F42" t="n">
-        <v>7.475222222222222</v>
+        <v>7.600555555555555</v>
       </c>
       <c r="G42" t="n">
-        <v>94.44444444444444</v>
+        <v>93.33333333333331</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -4186,16 +4186,16 @@
         <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F43" t="n">
-        <v>7.555222222222223</v>
+        <v>7.380000000000001</v>
       </c>
       <c r="G43" t="n">
         <v>95.55555555555556</v>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -4206,22 +4206,22 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>56</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7.520777777777778</v>
+      </c>
+      <c r="G44" t="n">
+        <v>98.88888888888889</v>
+      </c>
+      <c r="H44" t="n">
         <v>3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>57</v>
-      </c>
-      <c r="F44" t="n">
-        <v>7.471333333333333</v>
-      </c>
-      <c r="G44" t="n">
-        <v>96.66666666666669</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -4232,22 +4232,22 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F45" t="n">
-        <v>7.383333333333334</v>
+        <v>7.446888888888889</v>
       </c>
       <c r="G45" t="n">
-        <v>95.55555555555556</v>
+        <v>93.33333333333331</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -4258,19 +4258,19 @@
         <v>90</v>
       </c>
       <c r="C46" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F46" t="n">
-        <v>7.439555555555555</v>
+        <v>7.48811111111111</v>
       </c>
       <c r="G46" t="n">
-        <v>96.66666666666669</v>
+        <v>98.88888888888889</v>
       </c>
       <c r="H46" t="n">
         <v>2</v>
@@ -4284,22 +4284,22 @@
         <v>90</v>
       </c>
       <c r="C47" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F47" t="n">
-        <v>7.551222222222222</v>
+        <v>7.655</v>
       </c>
       <c r="G47" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -4310,22 +4310,22 @@
         <v>90</v>
       </c>
       <c r="C48" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F48" t="n">
-        <v>7.466555555555556</v>
+        <v>7.487111111111111</v>
       </c>
       <c r="G48" t="n">
-        <v>96.66666666666669</v>
+        <v>98.88888888888889</v>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -4336,22 +4336,22 @@
         <v>90</v>
       </c>
       <c r="C49" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F49" t="n">
-        <v>7.486111111111111</v>
+        <v>7.557222222222222</v>
       </c>
       <c r="G49" t="n">
-        <v>91.11111111111111</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -4362,19 +4362,19 @@
         <v>90</v>
       </c>
       <c r="C50" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F50" t="n">
-        <v>7.358111111111111</v>
+        <v>7.573777777777778</v>
       </c>
       <c r="G50" t="n">
-        <v>95.55555555555556</v>
+        <v>92.22222222222224</v>
       </c>
       <c r="H50" t="n">
         <v>3</v>
@@ -4388,22 +4388,22 @@
         <v>90</v>
       </c>
       <c r="C51" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F51" t="n">
-        <v>7.482666666666668</v>
+        <v>7.541444444444445</v>
       </c>
       <c r="G51" t="n">
-        <v>95.55555555555556</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -4414,19 +4414,19 @@
         <v>90</v>
       </c>
       <c r="C52" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F52" t="n">
-        <v>7.393777777777777</v>
+        <v>7.423333333333334</v>
       </c>
       <c r="G52" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H52" t="n">
         <v>5</v>
@@ -4440,19 +4440,19 @@
         <v>90</v>
       </c>
       <c r="C53" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F53" t="n">
-        <v>7.646888888888889</v>
+        <v>7.556555555555556</v>
       </c>
       <c r="G53" t="n">
-        <v>97.77777777777776</v>
+        <v>93.33333333333331</v>
       </c>
       <c r="H53" t="n">
         <v>3</v>
@@ -4466,22 +4466,22 @@
         <v>90</v>
       </c>
       <c r="C54" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>7.478222222222222</v>
+        <v>7.486333333333333</v>
       </c>
       <c r="G54" t="n">
-        <v>94.44444444444444</v>
+        <v>98.88888888888889</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -4492,19 +4492,19 @@
         <v>90</v>
       </c>
       <c r="C55" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>7.484444444444445</v>
+        <v>7.592555555555556</v>
       </c>
       <c r="G55" t="n">
-        <v>95.55555555555556</v>
+        <v>93.33333333333331</v>
       </c>
       <c r="H55" t="n">
         <v>2</v>
@@ -4518,19 +4518,19 @@
         <v>90</v>
       </c>
       <c r="C56" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E56" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F56" t="n">
-        <v>7.598333333333334</v>
+        <v>7.299222222222221</v>
       </c>
       <c r="G56" t="n">
-        <v>94.44444444444444</v>
+        <v>92.22222222222224</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
@@ -4544,22 +4544,22 @@
         <v>90</v>
       </c>
       <c r="C57" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>7.431444444444445</v>
+        <v>7.684555555555556</v>
       </c>
       <c r="G57" t="n">
-        <v>91.11111111111111</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -4570,22 +4570,22 @@
         <v>90</v>
       </c>
       <c r="C58" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F58" t="n">
-        <v>7.565777777777777</v>
+        <v>7.533888888888888</v>
       </c>
       <c r="G58" t="n">
-        <v>94.44444444444444</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -4596,22 +4596,22 @@
         <v>90</v>
       </c>
       <c r="C59" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F59" t="n">
-        <v>7.472</v>
+        <v>7.441222222222223</v>
       </c>
       <c r="G59" t="n">
-        <v>96.66666666666669</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -4622,22 +4622,22 @@
         <v>90</v>
       </c>
       <c r="C60" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D60" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" t="n">
+        <v>53</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7.597444444444444</v>
+      </c>
+      <c r="G60" t="n">
+        <v>92.22222222222224</v>
+      </c>
+      <c r="H60" t="n">
         <v>4</v>
-      </c>
-      <c r="E60" t="n">
-        <v>62</v>
-      </c>
-      <c r="F60" t="n">
-        <v>7.502555555555555</v>
-      </c>
-      <c r="G60" t="n">
-        <v>95.55555555555556</v>
-      </c>
-      <c r="H60" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -4648,22 +4648,22 @@
         <v>90</v>
       </c>
       <c r="C61" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F61" t="n">
-        <v>7.493222222222222</v>
+        <v>7.436888888888889</v>
       </c>
       <c r="G61" t="n">
-        <v>97.77777777777776</v>
+        <v>93.33333333333331</v>
       </c>
       <c r="H61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -4674,22 +4674,22 @@
         <v>90</v>
       </c>
       <c r="C62" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E62" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F62" t="n">
-        <v>7.543777777777779</v>
+        <v>7.389333333333333</v>
       </c>
       <c r="G62" t="n">
-        <v>97.77777777777776</v>
+        <v>92.22222222222224</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4700,22 +4700,22 @@
         <v>90</v>
       </c>
       <c r="C63" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F63" t="n">
-        <v>7.559777777777778</v>
+        <v>7.436111111111111</v>
       </c>
       <c r="G63" t="n">
-        <v>94.44444444444444</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -4726,22 +4726,22 @@
         <v>90</v>
       </c>
       <c r="C64" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F64" t="n">
-        <v>7.298999999999999</v>
+        <v>7.591666666666667</v>
       </c>
       <c r="G64" t="n">
-        <v>92.22222222222224</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4752,22 +4752,22 @@
         <v>90</v>
       </c>
       <c r="C65" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>7.521333333333333</v>
+        <v>7.528333333333332</v>
       </c>
       <c r="G65" t="n">
-        <v>97.77777777777776</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4784,10 +4784,10 @@
         <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F66" t="n">
-        <v>7.417555555555556</v>
+        <v>7.427444444444445</v>
       </c>
       <c r="G66" t="n">
         <v>94.44444444444444</v>
@@ -4804,22 +4804,22 @@
         <v>90</v>
       </c>
       <c r="C67" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D67" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" t="n">
+        <v>46</v>
+      </c>
+      <c r="F67" t="n">
+        <v>7.453666666666667</v>
+      </c>
+      <c r="G67" t="n">
+        <v>95.55555555555556</v>
+      </c>
+      <c r="H67" t="n">
         <v>3</v>
-      </c>
-      <c r="E67" t="n">
-        <v>52</v>
-      </c>
-      <c r="F67" t="n">
-        <v>7.577666666666666</v>
-      </c>
-      <c r="G67" t="n">
-        <v>96.66666666666669</v>
-      </c>
-      <c r="H67" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4830,22 +4830,22 @@
         <v>90</v>
       </c>
       <c r="C68" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E68" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F68" t="n">
-        <v>7.448111111111111</v>
+        <v>7.597888888888888</v>
       </c>
       <c r="G68" t="n">
-        <v>95.55555555555556</v>
+        <v>91.11111111111111</v>
       </c>
       <c r="H68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4856,22 +4856,22 @@
         <v>90</v>
       </c>
       <c r="C69" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F69" t="n">
-        <v>7.585666666666667</v>
+        <v>7.573</v>
       </c>
       <c r="G69" t="n">
-        <v>97.77777777777776</v>
+        <v>98.88888888888889</v>
       </c>
       <c r="H69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4882,22 +4882,22 @@
         <v>90</v>
       </c>
       <c r="C70" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E70" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F70" t="n">
-        <v>7.478666666666667</v>
+        <v>7.426111111111111</v>
       </c>
       <c r="G70" t="n">
-        <v>92.22222222222224</v>
+        <v>91.11111111111111</v>
       </c>
       <c r="H70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4908,22 +4908,22 @@
         <v>90</v>
       </c>
       <c r="C71" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F71" t="n">
-        <v>7.472333333333333</v>
+        <v>7.515444444444444</v>
       </c>
       <c r="G71" t="n">
-        <v>98.88888888888889</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4934,22 +4934,22 @@
         <v>90</v>
       </c>
       <c r="C72" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E72" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F72" t="n">
-        <v>7.563</v>
+        <v>7.459555555555555</v>
       </c>
       <c r="G72" t="n">
-        <v>100</v>
+        <v>91.11111111111111</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4960,22 +4960,22 @@
         <v>90</v>
       </c>
       <c r="C73" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F73" t="n">
-        <v>7.528333333333332</v>
+        <v>7.649555555555556</v>
       </c>
       <c r="G73" t="n">
-        <v>97.77777777777776</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4986,22 +4986,22 @@
         <v>90</v>
       </c>
       <c r="C74" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F74" t="n">
-        <v>7.401333333333333</v>
+        <v>7.478</v>
       </c>
       <c r="G74" t="n">
-        <v>98.88888888888889</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -5012,19 +5012,19 @@
         <v>90</v>
       </c>
       <c r="C75" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F75" t="n">
-        <v>7.360222222222221</v>
+        <v>7.594888888888889</v>
       </c>
       <c r="G75" t="n">
-        <v>95.55555555555556</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H75" t="n">
         <v>2</v>
@@ -5044,16 +5044,16 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F76" t="n">
-        <v>7.471888888888889</v>
+        <v>7.471444444444444</v>
       </c>
       <c r="G76" t="n">
         <v>96.66666666666669</v>
       </c>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -5064,22 +5064,22 @@
         <v>90</v>
       </c>
       <c r="C77" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F77" t="n">
-        <v>7.444888888888888</v>
+        <v>7.512777777777777</v>
       </c>
       <c r="G77" t="n">
-        <v>93.33333333333331</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -5090,22 +5090,22 @@
         <v>90</v>
       </c>
       <c r="C78" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
         <v>53</v>
       </c>
       <c r="F78" t="n">
-        <v>7.393444444444444</v>
+        <v>7.337000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>95.55555555555556</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -5116,22 +5116,22 @@
         <v>90</v>
       </c>
       <c r="C79" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F79" t="n">
-        <v>7.381888888888889</v>
+        <v>7.539888888888889</v>
       </c>
       <c r="G79" t="n">
-        <v>95.55555555555556</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -5142,22 +5142,22 @@
         <v>90</v>
       </c>
       <c r="C80" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F80" t="n">
-        <v>7.542777777777778</v>
+        <v>7.355888888888889</v>
       </c>
       <c r="G80" t="n">
-        <v>97.77777777777776</v>
+        <v>96.66666666666669</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -5168,22 +5168,22 @@
         <v>90</v>
       </c>
       <c r="C81" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D81" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F81" t="n">
-        <v>7.441444444444445</v>
+        <v>7.544111111111111</v>
       </c>
       <c r="G81" t="n">
-        <v>92.22222222222224</v>
+        <v>98.88888888888889</v>
       </c>
       <c r="H81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -5194,22 +5194,22 @@
         <v>90</v>
       </c>
       <c r="C82" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F82" t="n">
-        <v>7.400777777777778</v>
+        <v>7.505000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>98.88888888888889</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -5220,22 +5220,22 @@
         <v>90</v>
       </c>
       <c r="C83" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D83" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
         <v>55</v>
       </c>
       <c r="F83" t="n">
-        <v>7.510555555555556</v>
+        <v>7.434111111111112</v>
       </c>
       <c r="G83" t="n">
-        <v>90</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -5246,22 +5246,22 @@
         <v>90</v>
       </c>
       <c r="C84" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F84" t="n">
-        <v>7.470666666666667</v>
+        <v>7.573111111111111</v>
       </c>
       <c r="G84" t="n">
-        <v>94.44444444444444</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -5272,22 +5272,22 @@
         <v>90</v>
       </c>
       <c r="C85" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F85" t="n">
-        <v>7.485888888888889</v>
+        <v>7.363222222222223</v>
       </c>
       <c r="G85" t="n">
-        <v>98.88888888888889</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H85" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -5304,16 +5304,16 @@
         <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F86" t="n">
-        <v>7.626888888888889</v>
+        <v>7.506555555555556</v>
       </c>
       <c r="G86" t="n">
         <v>94.44444444444444</v>
       </c>
       <c r="H86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -5324,22 +5324,22 @@
         <v>90</v>
       </c>
       <c r="C87" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F87" t="n">
-        <v>7.544555555555555</v>
+        <v>7.500777777777778</v>
       </c>
       <c r="G87" t="n">
-        <v>95.55555555555556</v>
+        <v>98.88888888888889</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -5350,22 +5350,22 @@
         <v>90</v>
       </c>
       <c r="C88" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D88" t="n">
+        <v>6</v>
+      </c>
+      <c r="E88" t="n">
+        <v>47</v>
+      </c>
+      <c r="F88" t="n">
+        <v>7.537555555555556</v>
+      </c>
+      <c r="G88" t="n">
+        <v>93.33333333333331</v>
+      </c>
+      <c r="H88" t="n">
         <v>3</v>
-      </c>
-      <c r="E88" t="n">
-        <v>56</v>
-      </c>
-      <c r="F88" t="n">
-        <v>7.628777777777778</v>
-      </c>
-      <c r="G88" t="n">
-        <v>96.66666666666669</v>
-      </c>
-      <c r="H88" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -5376,22 +5376,22 @@
         <v>90</v>
       </c>
       <c r="C89" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E89" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F89" t="n">
-        <v>7.469666666666667</v>
+        <v>7.349888888888889</v>
       </c>
       <c r="G89" t="n">
-        <v>95.55555555555556</v>
+        <v>91.11111111111111</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5402,22 +5402,22 @@
         <v>90</v>
       </c>
       <c r="C90" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D90" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>7.656</v>
+        <v>7.517333333333334</v>
       </c>
       <c r="G90" t="n">
-        <v>90</v>
+        <v>93.33333333333331</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -5428,22 +5428,22 @@
         <v>90</v>
       </c>
       <c r="C91" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E91" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F91" t="n">
-        <v>7.434111111111112</v>
+        <v>7.630999999999999</v>
       </c>
       <c r="G91" t="n">
-        <v>97.77777777777776</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="H91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -5454,22 +5454,22 @@
         <v>90</v>
       </c>
       <c r="C92" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E92" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F92" t="n">
-        <v>7.54</v>
+        <v>7.49388888888889</v>
       </c>
       <c r="G92" t="n">
-        <v>96.66666666666669</v>
+        <v>92.22222222222224</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -5480,22 +5480,22 @@
         <v>90</v>
       </c>
       <c r="C93" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F93" t="n">
-        <v>7.534777777777777</v>
+        <v>7.396444444444445</v>
       </c>
       <c r="G93" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -5512,10 +5512,10 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F94" t="n">
-        <v>7.473222222222223</v>
+        <v>7.448111111111111</v>
       </c>
       <c r="G94" t="n">
         <v>92.22222222222224</v>
@@ -5532,22 +5532,22 @@
         <v>90</v>
       </c>
       <c r="C95" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D95" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E95" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F95" t="n">
-        <v>7.445333333333334</v>
+        <v>7.471888888888889</v>
       </c>
       <c r="G95" t="n">
-        <v>90</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -5558,22 +5558,22 @@
         <v>90</v>
       </c>
       <c r="C96" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E96" t="n">
         <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>7.315555555555555</v>
+        <v>7.531444444444445</v>
       </c>
       <c r="G96" t="n">
-        <v>92.22222222222224</v>
+        <v>88.88888888888889</v>
       </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -5584,22 +5584,22 @@
         <v>90</v>
       </c>
       <c r="C97" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E97" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F97" t="n">
-        <v>7.684555555555556</v>
+        <v>7.412333333333334</v>
       </c>
       <c r="G97" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5610,22 +5610,22 @@
         <v>90</v>
       </c>
       <c r="C98" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E98" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F98" t="n">
-        <v>7.578333333333333</v>
+        <v>7.399444444444445</v>
       </c>
       <c r="G98" t="n">
-        <v>92.22222222222224</v>
+        <v>91.11111111111111</v>
       </c>
       <c r="H98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -5636,22 +5636,22 @@
         <v>90</v>
       </c>
       <c r="C99" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F99" t="n">
-        <v>7.369444444444444</v>
+        <v>7.468555555555555</v>
       </c>
       <c r="G99" t="n">
-        <v>94.44444444444444</v>
+        <v>97.77777777777776</v>
       </c>
       <c r="H99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -5662,22 +5662,22 @@
         <v>90</v>
       </c>
       <c r="C100" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E100" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F100" t="n">
-        <v>7.531444444444445</v>
+        <v>7.405555555555556</v>
       </c>
       <c r="G100" t="n">
-        <v>97.77777777777776</v>
+        <v>94.44444444444444</v>
       </c>
       <c r="H100" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
@@ -5688,22 +5688,22 @@
         <v>90</v>
       </c>
       <c r="C101" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E101" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F101" t="n">
-        <v>7.622555555555556</v>
+        <v>7.574666666666667</v>
       </c>
       <c r="G101" t="n">
-        <v>96.66666666666669</v>
+        <v>95.55555555555556</v>
       </c>
       <c r="H101" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5757,13 +5757,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>75184</v>
+        <v>88247</v>
       </c>
       <c r="C2" t="n">
-        <v>10024.53</v>
+        <v>11766.27</v>
       </c>
       <c r="D2" t="n">
-        <v>65159.47</v>
+        <v>76480.73</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
@@ -5777,19 +5777,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>36174</v>
+        <v>54032</v>
       </c>
       <c r="C3" t="n">
-        <v>7234.8</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>28939.2</v>
+        <v>54032</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5797,19 +5797,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>60978</v>
+        <v>43524</v>
       </c>
       <c r="C4" t="n">
-        <v>14228.2</v>
+        <v>5803.2</v>
       </c>
       <c r="D4" t="n">
-        <v>46749.8</v>
+        <v>37720.8</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -5817,13 +5817,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>83470</v>
+        <v>56257</v>
       </c>
       <c r="C5" t="n">
-        <v>2782.33</v>
+        <v>1875.23</v>
       </c>
       <c r="D5" t="n">
-        <v>80687.67</v>
+        <v>54381.77</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -5837,19 +5837,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>70366</v>
+        <v>33224</v>
       </c>
       <c r="C6" t="n">
-        <v>4691.07</v>
+        <v>4429.87</v>
       </c>
       <c r="D6" t="n">
-        <v>65674.92999999999</v>
+        <v>28794.13</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -5857,19 +5857,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>54085</v>
+        <v>87885</v>
       </c>
       <c r="C7" t="n">
-        <v>3605.67</v>
+        <v>11718</v>
       </c>
       <c r="D7" t="n">
-        <v>50479.33</v>
+        <v>76167</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -5877,19 +5877,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>53794</v>
+        <v>49895</v>
       </c>
       <c r="C8" t="n">
-        <v>3586.27</v>
+        <v>4989.5</v>
       </c>
       <c r="D8" t="n">
-        <v>50207.73</v>
+        <v>44905.5</v>
       </c>
       <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
         <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5897,19 +5897,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>88985</v>
+        <v>54707</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1823.57</v>
       </c>
       <c r="D9" t="n">
-        <v>88985</v>
+        <v>52883.43</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5917,19 +5917,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>49548</v>
+        <v>40748</v>
       </c>
       <c r="C10" t="n">
-        <v>6606.4</v>
+        <v>2716.53</v>
       </c>
       <c r="D10" t="n">
-        <v>42941.6</v>
+        <v>38031.47</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5937,19 +5937,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>88528</v>
+        <v>55654</v>
       </c>
       <c r="C11" t="n">
-        <v>11803.73</v>
+        <v>3710.27</v>
       </c>
       <c r="D11" t="n">
-        <v>76724.27</v>
+        <v>51943.73</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5957,19 +5957,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>68201</v>
+        <v>30943</v>
       </c>
       <c r="C12" t="n">
-        <v>4546.73</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>63654.27</v>
+        <v>30943</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5977,13 +5977,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>69715</v>
+        <v>49482</v>
       </c>
       <c r="C13" t="n">
-        <v>6971.5</v>
+        <v>4948.2</v>
       </c>
       <c r="D13" t="n">
-        <v>62743.5</v>
+        <v>44533.8</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -5997,19 +5997,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>63506</v>
+        <v>76696</v>
       </c>
       <c r="C14" t="n">
-        <v>2116.87</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>61389.13</v>
+        <v>76696</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -6017,19 +6017,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>68171</v>
+        <v>36331</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2422.07</v>
       </c>
       <c r="D15" t="n">
-        <v>68171</v>
+        <v>33908.93</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -6037,19 +6037,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>40801</v>
+        <v>47466</v>
       </c>
       <c r="C16" t="n">
-        <v>5440.13</v>
+        <v>3164.4</v>
       </c>
       <c r="D16" t="n">
-        <v>35360.87</v>
+        <v>44301.6</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -6057,19 +6057,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>82914</v>
+        <v>69886</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>18636.27</v>
       </c>
       <c r="D17" t="n">
-        <v>82914</v>
+        <v>51249.73</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -6077,19 +6077,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>49754</v>
+        <v>66537</v>
       </c>
       <c r="C18" t="n">
-        <v>3316.93</v>
+        <v>6653.7</v>
       </c>
       <c r="D18" t="n">
-        <v>46437.07</v>
+        <v>59883.3</v>
       </c>
       <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
         <v>3</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -6097,19 +6097,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>36971</v>
+        <v>71141</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>7114.1</v>
       </c>
       <c r="D19" t="n">
-        <v>36971</v>
+        <v>64026.9</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -6117,19 +6117,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>77879</v>
+        <v>58486</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>7798.13</v>
       </c>
       <c r="D20" t="n">
-        <v>77879</v>
+        <v>50687.87</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -6137,13 +6137,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>71492</v>
+        <v>48913</v>
       </c>
       <c r="C21" t="n">
-        <v>2383.07</v>
+        <v>1630.43</v>
       </c>
       <c r="D21" t="n">
-        <v>69108.92999999999</v>
+        <v>47282.57</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -6157,19 +6157,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>42744</v>
+        <v>49296</v>
       </c>
       <c r="C22" t="n">
-        <v>7124</v>
+        <v>3286.4</v>
       </c>
       <c r="D22" t="n">
-        <v>35620</v>
+        <v>46009.6</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -6177,19 +6177,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>85740</v>
+        <v>73751</v>
       </c>
       <c r="C23" t="n">
-        <v>8574</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>77166</v>
+        <v>73751</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -6197,19 +6197,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>67234</v>
+        <v>79194</v>
       </c>
       <c r="C24" t="n">
-        <v>6723.4</v>
+        <v>2639.8</v>
       </c>
       <c r="D24" t="n">
-        <v>60510.6</v>
+        <v>76554.2</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -6217,19 +6217,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>65911</v>
+        <v>84706</v>
       </c>
       <c r="C25" t="n">
-        <v>6591.1</v>
+        <v>5647.07</v>
       </c>
       <c r="D25" t="n">
-        <v>59319.9</v>
+        <v>79058.92999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -6237,19 +6237,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>71912</v>
+        <v>85708</v>
       </c>
       <c r="C26" t="n">
-        <v>4794.13</v>
+        <v>2856.93</v>
       </c>
       <c r="D26" t="n">
-        <v>67117.87</v>
+        <v>82851.07000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -6257,19 +6257,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>87456</v>
+        <v>89391</v>
       </c>
       <c r="C27" t="n">
-        <v>8745.6</v>
+        <v>5959.4</v>
       </c>
       <c r="D27" t="n">
-        <v>78710.39999999999</v>
+        <v>83431.60000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -6277,19 +6277,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>58043</v>
+        <v>72545</v>
       </c>
       <c r="C28" t="n">
-        <v>9673.83</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>48369.17</v>
+        <v>72545</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -6297,13 +6297,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>85121</v>
+        <v>30161</v>
       </c>
       <c r="C29" t="n">
-        <v>2837.37</v>
+        <v>1005.37</v>
       </c>
       <c r="D29" t="n">
-        <v>82283.63</v>
+        <v>29155.63</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -6317,13 +6317,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>77542</v>
+        <v>69412</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>77542</v>
+        <v>69412</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -6337,13 +6337,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>86960</v>
+        <v>79608</v>
       </c>
       <c r="C31" t="n">
-        <v>2898.67</v>
+        <v>2653.6</v>
       </c>
       <c r="D31" t="n">
-        <v>84061.33</v>
+        <v>76954.39999999999</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -6357,19 +6357,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>85113</v>
+        <v>42896</v>
       </c>
       <c r="C32" t="n">
-        <v>5674.2</v>
+        <v>1429.87</v>
       </c>
       <c r="D32" t="n">
-        <v>79438.8</v>
+        <v>41466.13</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -6377,19 +6377,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>72502</v>
+        <v>70669</v>
       </c>
       <c r="C33" t="n">
-        <v>7250.2</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>65251.8</v>
+        <v>70669</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -6397,19 +6397,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>89260</v>
+        <v>47595</v>
       </c>
       <c r="C34" t="n">
-        <v>8926</v>
+        <v>1586.5</v>
       </c>
       <c r="D34" t="n">
-        <v>80334</v>
+        <v>46008.5</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -6417,13 +6417,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>41082</v>
+        <v>72835</v>
       </c>
       <c r="C35" t="n">
-        <v>4108.2</v>
+        <v>7283.5</v>
       </c>
       <c r="D35" t="n">
-        <v>36973.8</v>
+        <v>65551.5</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
@@ -6437,19 +6437,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>58307</v>
+        <v>41176</v>
       </c>
       <c r="C36" t="n">
-        <v>1943.57</v>
+        <v>2745.07</v>
       </c>
       <c r="D36" t="n">
-        <v>56363.43</v>
+        <v>38430.93</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -6457,19 +6457,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>82521</v>
+        <v>76468</v>
       </c>
       <c r="C37" t="n">
-        <v>13753.5</v>
+        <v>2548.93</v>
       </c>
       <c r="D37" t="n">
-        <v>68767.5</v>
+        <v>73919.07000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -6477,19 +6477,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>67223</v>
+        <v>88707</v>
       </c>
       <c r="C38" t="n">
-        <v>2240.77</v>
+        <v>8870.700000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>64982.23</v>
+        <v>79836.3</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -6497,19 +6497,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>30617</v>
+        <v>49070</v>
       </c>
       <c r="C39" t="n">
-        <v>1020.57</v>
+        <v>8178.33</v>
       </c>
       <c r="D39" t="n">
-        <v>29596.43</v>
+        <v>40891.67</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -6517,19 +6517,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>35021</v>
+        <v>31493</v>
       </c>
       <c r="C40" t="n">
-        <v>4669.47</v>
+        <v>1049.77</v>
       </c>
       <c r="D40" t="n">
-        <v>30351.53</v>
+        <v>30443.23</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -6537,19 +6537,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>78190</v>
+        <v>41384</v>
       </c>
       <c r="C41" t="n">
-        <v>2606.33</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>75583.67</v>
+        <v>41384</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -6557,19 +6557,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>53838</v>
+        <v>85604</v>
       </c>
       <c r="C42" t="n">
-        <v>7178.4</v>
+        <v>14267.33</v>
       </c>
       <c r="D42" t="n">
-        <v>46659.6</v>
+        <v>71336.67</v>
       </c>
       <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="n">
         <v>5</v>
-      </c>
-      <c r="F42" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -6577,19 +6577,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>54168</v>
+        <v>48219</v>
       </c>
       <c r="C43" t="n">
-        <v>5416.8</v>
+        <v>1607.3</v>
       </c>
       <c r="D43" t="n">
-        <v>48751.2</v>
+        <v>46611.7</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -6597,19 +6597,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>83808</v>
+        <v>45393</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>3026.2</v>
       </c>
       <c r="D44" t="n">
-        <v>83808</v>
+        <v>42366.8</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -6617,19 +6617,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>42494</v>
+        <v>65740</v>
       </c>
       <c r="C45" t="n">
-        <v>2832.93</v>
+        <v>2191.33</v>
       </c>
       <c r="D45" t="n">
-        <v>39661.07</v>
+        <v>63548.67</v>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -6637,13 +6637,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>40304</v>
+        <v>66905</v>
       </c>
       <c r="C46" t="n">
-        <v>1343.47</v>
+        <v>2230.17</v>
       </c>
       <c r="D46" t="n">
-        <v>38960.53</v>
+        <v>64674.83</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
@@ -6657,19 +6657,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>40224</v>
+        <v>61022</v>
       </c>
       <c r="C47" t="n">
-        <v>1340.8</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>38883.2</v>
+        <v>61022</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -6677,19 +6677,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>79188</v>
+        <v>35173</v>
       </c>
       <c r="C48" t="n">
-        <v>7918.8</v>
+        <v>5862.17</v>
       </c>
       <c r="D48" t="n">
-        <v>71269.2</v>
+        <v>29310.83</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -6697,19 +6697,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>56279</v>
+        <v>78208</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>7820.8</v>
       </c>
       <c r="D49" t="n">
-        <v>56279</v>
+        <v>70387.2</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -6717,13 +6717,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>33537</v>
+        <v>85644</v>
       </c>
       <c r="C50" t="n">
-        <v>2235.8</v>
+        <v>5709.6</v>
       </c>
       <c r="D50" t="n">
-        <v>31301.2</v>
+        <v>79934.39999999999</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
@@ -6737,19 +6737,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>83619</v>
+        <v>53051</v>
       </c>
       <c r="C51" t="n">
-        <v>8361.9</v>
+        <v>3536.73</v>
       </c>
       <c r="D51" t="n">
-        <v>75257.10000000001</v>
+        <v>49514.27</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -6757,13 +6757,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>59975</v>
+        <v>45878</v>
       </c>
       <c r="C52" t="n">
-        <v>7996.67</v>
+        <v>6117.07</v>
       </c>
       <c r="D52" t="n">
-        <v>51978.33</v>
+        <v>39760.93</v>
       </c>
       <c r="E52" t="n">
         <v>5</v>
@@ -6777,13 +6777,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>57409</v>
+        <v>86429</v>
       </c>
       <c r="C53" t="n">
-        <v>3827.27</v>
+        <v>5761.93</v>
       </c>
       <c r="D53" t="n">
-        <v>53581.73</v>
+        <v>80667.07000000001</v>
       </c>
       <c r="E53" t="n">
         <v>3</v>
@@ -6797,19 +6797,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>80477</v>
+        <v>76386</v>
       </c>
       <c r="C54" t="n">
-        <v>2682.57</v>
+        <v>10184.8</v>
       </c>
       <c r="D54" t="n">
-        <v>77794.42999999999</v>
+        <v>66201.2</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -6817,13 +6817,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>65476</v>
+        <v>77096</v>
       </c>
       <c r="C55" t="n">
-        <v>2182.53</v>
+        <v>2569.87</v>
       </c>
       <c r="D55" t="n">
-        <v>63293.47</v>
+        <v>74526.13</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
@@ -6837,13 +6837,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>87091</v>
+        <v>58146</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>87091</v>
+        <v>58146</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -6857,19 +6857,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>63112</v>
+        <v>46364</v>
       </c>
       <c r="C57" t="n">
-        <v>6311.2</v>
+        <v>1545.47</v>
       </c>
       <c r="D57" t="n">
-        <v>56800.8</v>
+        <v>44818.53</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -6877,19 +6877,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>73795</v>
+        <v>69678</v>
       </c>
       <c r="C58" t="n">
-        <v>2459.83</v>
+        <v>4645.2</v>
       </c>
       <c r="D58" t="n">
-        <v>71335.17</v>
+        <v>65032.8</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -6897,19 +6897,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>44372</v>
+        <v>57944</v>
       </c>
       <c r="C59" t="n">
-        <v>2958.13</v>
+        <v>5794.4</v>
       </c>
       <c r="D59" t="n">
-        <v>41413.87</v>
+        <v>52149.6</v>
       </c>
       <c r="E59" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" t="n">
         <v>3</v>
-      </c>
-      <c r="F59" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -6917,19 +6917,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>76265</v>
+        <v>71744</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>7174.4</v>
       </c>
       <c r="D60" t="n">
-        <v>76265</v>
+        <v>64569.6</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -6937,19 +6937,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>70367</v>
+        <v>55673</v>
       </c>
       <c r="C61" t="n">
-        <v>11727.83</v>
+        <v>1855.77</v>
       </c>
       <c r="D61" t="n">
-        <v>58639.17</v>
+        <v>53817.23</v>
       </c>
       <c r="E61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -6957,19 +6957,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>75907</v>
+        <v>33081</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>3308.1</v>
       </c>
       <c r="D62" t="n">
-        <v>75907</v>
+        <v>29772.9</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -6977,19 +6977,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>64036</v>
+        <v>82042</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>8204.200000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>64036</v>
+        <v>73837.8</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -6997,19 +6997,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>81046</v>
+        <v>41265</v>
       </c>
       <c r="C64" t="n">
-        <v>5403.07</v>
+        <v>1375.5</v>
       </c>
       <c r="D64" t="n">
-        <v>75642.92999999999</v>
+        <v>39889.5</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -7017,19 +7017,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>32316</v>
+        <v>37308</v>
       </c>
       <c r="C65" t="n">
-        <v>4308.8</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>28007.2</v>
+        <v>37308</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -7037,13 +7037,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>84181</v>
+        <v>77352</v>
       </c>
       <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>84181</v>
+        <v>77352</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -7057,19 +7057,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>79502</v>
+        <v>38434</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>2562.27</v>
       </c>
       <c r="D67" t="n">
-        <v>79502</v>
+        <v>35871.73</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -7077,19 +7077,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>30647</v>
+        <v>71794</v>
       </c>
       <c r="C68" t="n">
-        <v>2043.13</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>28603.87</v>
+        <v>71794</v>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -7097,19 +7097,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>67049</v>
+        <v>53223</v>
       </c>
       <c r="C69" t="n">
-        <v>4469.93</v>
+        <v>1774.1</v>
       </c>
       <c r="D69" t="n">
-        <v>62579.07</v>
+        <v>51448.9</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -7117,19 +7117,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>50625</v>
+        <v>79907</v>
       </c>
       <c r="C70" t="n">
-        <v>5062.5</v>
+        <v>5327.13</v>
       </c>
       <c r="D70" t="n">
-        <v>45562.5</v>
+        <v>74579.87</v>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -7137,19 +7137,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>83190</v>
+        <v>61437</v>
       </c>
       <c r="C71" t="n">
-        <v>5546</v>
+        <v>2047.9</v>
       </c>
       <c r="D71" t="n">
-        <v>77644</v>
+        <v>59389.1</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -7157,19 +7157,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>30121</v>
+        <v>30966</v>
       </c>
       <c r="C72" t="n">
-        <v>1004.03</v>
+        <v>2064.4</v>
       </c>
       <c r="D72" t="n">
-        <v>29116.97</v>
+        <v>28901.6</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -7177,19 +7177,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>88754</v>
+        <v>46876</v>
       </c>
       <c r="C73" t="n">
-        <v>8875.4</v>
+        <v>1562.53</v>
       </c>
       <c r="D73" t="n">
-        <v>79878.60000000001</v>
+        <v>45313.47</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -7197,19 +7197,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>87142</v>
+        <v>47117</v>
       </c>
       <c r="C74" t="n">
-        <v>5809.47</v>
+        <v>4711.7</v>
       </c>
       <c r="D74" t="n">
-        <v>81332.53</v>
+        <v>42405.3</v>
       </c>
       <c r="E74" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" t="n">
         <v>3</v>
-      </c>
-      <c r="F74" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -7217,13 +7217,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>54179</v>
+        <v>36577</v>
       </c>
       <c r="C75" t="n">
-        <v>1805.97</v>
+        <v>1219.23</v>
       </c>
       <c r="D75" t="n">
-        <v>52373.03</v>
+        <v>35357.77</v>
       </c>
       <c r="E75" t="n">
         <v>2</v>
@@ -7237,19 +7237,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>51914</v>
+        <v>60851</v>
       </c>
       <c r="C76" t="n">
-        <v>5191.4</v>
+        <v>12170.2</v>
       </c>
       <c r="D76" t="n">
-        <v>46722.6</v>
+        <v>48680.8</v>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -7257,19 +7257,19 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>31154</v>
+        <v>83942</v>
       </c>
       <c r="C77" t="n">
-        <v>3115.4</v>
+        <v>2798.07</v>
       </c>
       <c r="D77" t="n">
-        <v>28038.6</v>
+        <v>81143.92999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -7277,19 +7277,19 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>56461</v>
+        <v>49866</v>
       </c>
       <c r="C78" t="n">
-        <v>1882.03</v>
+        <v>3324.4</v>
       </c>
       <c r="D78" t="n">
-        <v>54578.97</v>
+        <v>46541.6</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -7297,19 +7297,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>52170</v>
+        <v>68289</v>
       </c>
       <c r="C79" t="n">
-        <v>3478</v>
+        <v>9105.200000000001</v>
       </c>
       <c r="D79" t="n">
-        <v>48692</v>
+        <v>59183.8</v>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -7317,19 +7317,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>70083</v>
+        <v>71987</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>14397.4</v>
       </c>
       <c r="D80" t="n">
-        <v>70083</v>
+        <v>57589.6</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -7337,19 +7337,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>62641</v>
+        <v>71502</v>
       </c>
       <c r="C81" t="n">
-        <v>8352.129999999999</v>
+        <v>2383.4</v>
       </c>
       <c r="D81" t="n">
-        <v>54288.87</v>
+        <v>69118.60000000001</v>
       </c>
       <c r="E81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -7357,19 +7357,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>87293</v>
+        <v>68315</v>
       </c>
       <c r="C82" t="n">
-        <v>2909.77</v>
+        <v>11385.83</v>
       </c>
       <c r="D82" t="n">
-        <v>84383.23</v>
+        <v>56929.17</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -7377,19 +7377,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>48344</v>
+        <v>84596</v>
       </c>
       <c r="C83" t="n">
-        <v>3222.93</v>
+        <v>11279.47</v>
       </c>
       <c r="D83" t="n">
-        <v>45121.07</v>
+        <v>73316.53</v>
       </c>
       <c r="E83" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -7397,19 +7397,19 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>61944</v>
+        <v>47146</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>4714.6</v>
       </c>
       <c r="D84" t="n">
-        <v>61944</v>
+        <v>42431.4</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -7417,19 +7417,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>30903</v>
+        <v>56753</v>
       </c>
       <c r="C85" t="n">
-        <v>5150.5</v>
+        <v>3783.53</v>
       </c>
       <c r="D85" t="n">
-        <v>25752.5</v>
+        <v>52969.47</v>
       </c>
       <c r="E85" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -7437,19 +7437,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>76849</v>
+        <v>78327</v>
       </c>
       <c r="C86" t="n">
-        <v>10246.53</v>
+        <v>15665.4</v>
       </c>
       <c r="D86" t="n">
-        <v>66602.47</v>
+        <v>62661.6</v>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
@@ -7457,19 +7457,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>63944</v>
+        <v>81753</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>2725.1</v>
       </c>
       <c r="D87" t="n">
-        <v>63944</v>
+        <v>79027.89999999999</v>
       </c>
       <c r="E87" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" t="n">
         <v>1</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -7477,19 +7477,19 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>33511</v>
+        <v>54419</v>
       </c>
       <c r="C88" t="n">
-        <v>1117.03</v>
+        <v>3627.93</v>
       </c>
       <c r="D88" t="n">
-        <v>32393.97</v>
+        <v>50791.07</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -7497,16 +7497,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>52552</v>
+        <v>84308</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>52552</v>
+        <v>84308</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -7517,19 +7517,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>87078</v>
+        <v>66491</v>
       </c>
       <c r="C90" t="n">
-        <v>2902.6</v>
+        <v>6649.1</v>
       </c>
       <c r="D90" t="n">
-        <v>84175.39999999999</v>
+        <v>59841.9</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -7537,19 +7537,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>32271</v>
+        <v>70862</v>
       </c>
       <c r="C91" t="n">
-        <v>2151.4</v>
+        <v>2362.07</v>
       </c>
       <c r="D91" t="n">
-        <v>30119.6</v>
+        <v>68499.92999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -7557,19 +7557,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>46925</v>
+        <v>41653</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>6942.17</v>
       </c>
       <c r="D92" t="n">
-        <v>46925</v>
+        <v>34710.83</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -7577,19 +7577,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>72139</v>
+        <v>58661</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>1955.37</v>
       </c>
       <c r="D93" t="n">
-        <v>72139</v>
+        <v>56705.63</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -7597,13 +7597,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>47020</v>
+        <v>48467</v>
       </c>
       <c r="C94" t="n">
-        <v>1567.33</v>
+        <v>1615.57</v>
       </c>
       <c r="D94" t="n">
-        <v>45452.67</v>
+        <v>46851.43</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
@@ -7617,19 +7617,19 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>64226</v>
+        <v>70134</v>
       </c>
       <c r="C95" t="n">
-        <v>8563.469999999999</v>
+        <v>2337.8</v>
       </c>
       <c r="D95" t="n">
-        <v>55662.53</v>
+        <v>67796.2</v>
       </c>
       <c r="E95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -7637,19 +7637,19 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>32590</v>
+        <v>35500</v>
       </c>
       <c r="C96" t="n">
-        <v>2172.67</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>30417.33</v>
+        <v>35500</v>
       </c>
       <c r="E96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -7657,19 +7657,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>52125</v>
+        <v>34825</v>
       </c>
       <c r="C97" t="n">
-        <v>3475</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>48650</v>
+        <v>34825</v>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -7677,19 +7677,19 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>31927</v>
+        <v>40117</v>
       </c>
       <c r="C98" t="n">
-        <v>3192.7</v>
+        <v>1337.23</v>
       </c>
       <c r="D98" t="n">
-        <v>28734.3</v>
+        <v>38779.77</v>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -7697,19 +7697,19 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>60323</v>
+        <v>55542</v>
       </c>
       <c r="C99" t="n">
-        <v>6032.3</v>
+        <v>1851.4</v>
       </c>
       <c r="D99" t="n">
-        <v>54290.7</v>
+        <v>53690.6</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -7717,19 +7717,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>42630</v>
+        <v>48136</v>
       </c>
       <c r="C100" t="n">
-        <v>4263</v>
+        <v>11231.73</v>
       </c>
       <c r="D100" t="n">
-        <v>38367</v>
+        <v>36904.27</v>
       </c>
       <c r="E100" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -7737,19 +7737,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>67950</v>
+        <v>37705</v>
       </c>
       <c r="C101" t="n">
-        <v>6795</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>61155</v>
+        <v>37705</v>
       </c>
       <c r="E101" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
